--- a/Indicador_Atendidos_Hipertencion_Meta_Terapeutica_2025.xlsx
+++ b/Indicador_Atendidos_Hipertencion_Meta_Terapeutica_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\proyectos_python\DashboardExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C22C8B8-0B43-4C3B-B750-FB140ED541BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91ED42E-34CE-4AF9-8054-D05FEA561DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-48" yWindow="-48" windowWidth="23136" windowHeight="12336" xr2:uid="{5FDAB1C1-EE38-4D0A-86B0-D4C4E4EDD931}"/>
   </bookViews>
@@ -2816,6 +2816,7 @@
         <v>392</v>
       </c>
       <c r="E98" s="5">
+        <f>C98/D98</f>
         <v>0.67602040816326525</v>
       </c>
       <c r="F98" s="3" t="s">
@@ -2839,6 +2840,7 @@
         <v>410</v>
       </c>
       <c r="E99" s="5">
+        <f t="shared" ref="E99:E121" si="0">C99/D99</f>
         <v>0.62926829268292683</v>
       </c>
       <c r="F99" s="3" t="s">
@@ -2862,6 +2864,7 @@
         <v>351</v>
       </c>
       <c r="E100" s="5">
+        <f t="shared" si="0"/>
         <v>0.60683760683760679</v>
       </c>
       <c r="F100" s="3" t="s">
@@ -2885,6 +2888,7 @@
         <v>213</v>
       </c>
       <c r="E101" s="5">
+        <f t="shared" si="0"/>
         <v>0.59624413145539901</v>
       </c>
       <c r="F101" s="3" t="s">
@@ -2908,6 +2912,7 @@
         <v>207</v>
       </c>
       <c r="E102" s="5">
+        <f t="shared" si="0"/>
         <v>0.58454106280193241</v>
       </c>
       <c r="F102" s="3" t="s">
@@ -2931,6 +2936,7 @@
         <v>315</v>
       </c>
       <c r="E103" s="5">
+        <f t="shared" si="0"/>
         <v>0.580952380952381</v>
       </c>
       <c r="F103" s="3" t="s">
@@ -2954,6 +2960,7 @@
         <v>477</v>
       </c>
       <c r="E104" s="5">
+        <f t="shared" si="0"/>
         <v>0.5765199161425576</v>
       </c>
       <c r="F104" s="3" t="s">
@@ -2977,6 +2984,7 @@
         <v>422</v>
       </c>
       <c r="E105" s="5">
+        <f t="shared" si="0"/>
         <v>0.53080568720379151</v>
       </c>
       <c r="F105" s="3" t="s">
@@ -3000,6 +3008,7 @@
         <v>205</v>
       </c>
       <c r="E106" s="5">
+        <f t="shared" si="0"/>
         <v>0.48780487804878048</v>
       </c>
       <c r="F106" s="3" t="s">
@@ -3023,6 +3032,7 @@
         <v>386</v>
       </c>
       <c r="E107" s="5">
+        <f t="shared" si="0"/>
         <v>0.46113989637305697</v>
       </c>
       <c r="F107" s="3" t="s">
@@ -3046,6 +3056,7 @@
         <v>204</v>
       </c>
       <c r="E108" s="5">
+        <f t="shared" si="0"/>
         <v>0.44117647058823528</v>
       </c>
       <c r="F108" s="3" t="s">
@@ -3069,6 +3080,7 @@
         <v>199</v>
       </c>
       <c r="E109" s="5">
+        <f t="shared" si="0"/>
         <v>0.35678391959798994</v>
       </c>
       <c r="F109" s="3" t="s">
@@ -3086,13 +3098,14 @@
         <v>3</v>
       </c>
       <c r="C110" s="1">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="D110" s="1">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="E110" s="5">
-        <v>0.67758186397984888</v>
+        <f t="shared" si="0"/>
+        <v>0.70123456790123462</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>29</v>
@@ -3109,13 +3122,14 @@
         <v>4</v>
       </c>
       <c r="C111" s="1">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="D111" s="1">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E111" s="5">
-        <v>0.61592505854800939</v>
+        <f t="shared" si="0"/>
+        <v>0.64801864801864806</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>29</v>
@@ -3132,13 +3146,14 @@
         <v>5</v>
       </c>
       <c r="C112" s="1">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="D112" s="1">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="E112" s="5">
-        <v>0.59890109890109888</v>
+        <f t="shared" si="0"/>
+        <v>0.64247311827956988</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>29</v>
@@ -3152,16 +3167,17 @@
         <v>4</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C113" s="1">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D113" s="1">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E113" s="5">
-        <v>0.59090909090909094</v>
+        <f t="shared" si="0"/>
+        <v>0.61860465116279073</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>29</v>
@@ -3175,16 +3191,17 @@
         <v>5</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C114" s="1">
-        <v>280</v>
+        <v>136</v>
       </c>
       <c r="D114" s="1">
-        <v>486</v>
+        <v>221</v>
       </c>
       <c r="E114" s="5">
-        <v>0.5761316872427984</v>
+        <f t="shared" si="0"/>
+        <v>0.61538461538461542</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>29</v>
@@ -3198,16 +3215,17 @@
         <v>6</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C115" s="1">
-        <v>123</v>
+        <v>300</v>
       </c>
       <c r="D115" s="1">
-        <v>214</v>
+        <v>491</v>
       </c>
       <c r="E115" s="5">
-        <v>0.57476635514018692</v>
+        <f t="shared" si="0"/>
+        <v>0.61099796334012224</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>29</v>
@@ -3224,13 +3242,14 @@
         <v>8</v>
       </c>
       <c r="C116" s="1">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="D116" s="1">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="E116" s="5">
-        <v>0.56060606060606055</v>
+        <f t="shared" si="0"/>
+        <v>0.58407079646017701</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>29</v>
@@ -3247,13 +3266,14 @@
         <v>10</v>
       </c>
       <c r="C117" s="1">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="D117" s="1">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E117" s="5">
-        <v>0.52447552447552448</v>
+        <f t="shared" si="0"/>
+        <v>0.54756380510440839</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>29</v>
@@ -3267,16 +3287,17 @@
         <v>9</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C118" s="1">
-        <v>100</v>
+        <v>203</v>
       </c>
       <c r="D118" s="1">
-        <v>210</v>
+        <v>408</v>
       </c>
       <c r="E118" s="5">
-        <v>0.47619047619047616</v>
+        <f t="shared" si="0"/>
+        <v>0.49754901960784315</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>29</v>
@@ -3290,16 +3311,17 @@
         <v>10</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C119" s="1">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="D119" s="1">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="E119" s="5">
-        <v>0.44878048780487806</v>
+        <f t="shared" si="0"/>
+        <v>0.49082568807339449</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>29</v>
@@ -3313,16 +3335,17 @@
         <v>11</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C120" s="1">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="D120" s="1">
-        <v>406</v>
+        <v>213</v>
       </c>
       <c r="E120" s="5">
-        <v>0.44827586206896552</v>
+        <f t="shared" si="0"/>
+        <v>0.460093896713615</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>29</v>
@@ -3339,13 +3362,14 @@
         <v>14</v>
       </c>
       <c r="C121" s="1">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D121" s="1">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E121" s="5">
-        <v>0.35499999999999998</v>
+        <f t="shared" si="0"/>
+        <v>0.3910891089108911</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>29</v>
